--- a/public/templates/SY2 Sem 4.xlsx
+++ b/public/templates/SY2 Sem 4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\WT DBMS CIE Project\Sample Excel Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\Automated Academic Report System\dist\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EC462F-EABA-496E-84AA-5EDF8C25B92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466DE359-C70A-47F5-BF15-629021B6D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{9825C9CF-F468-4764-ACEF-73A7F80F2223}"/>
   </bookViews>
@@ -1676,13 +1676,13 @@
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="8" width="42.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.7" x14ac:dyDescent="0.35">
@@ -1914,6 +1914,11 @@
       <c r="H11" s="9" t="s">
         <v>244</v>
       </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
@@ -1925,13 +1930,26 @@
       <c r="C12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="11">
+        <v>14</v>
+      </c>
+      <c r="E12" s="11">
+        <v>9</v>
+      </c>
+      <c r="F12" s="11">
+        <v>10</v>
+      </c>
+      <c r="G12" s="11">
+        <v>7</v>
+      </c>
       <c r="H12" s="14" t="s">
         <v>169</v>
       </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
@@ -1943,13 +1961,26 @@
       <c r="C13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="11">
+        <v>16</v>
+      </c>
+      <c r="E13" s="11">
+        <v>8</v>
+      </c>
+      <c r="F13" s="11">
+        <v>10</v>
+      </c>
+      <c r="G13" s="11">
+        <v>8</v>
+      </c>
       <c r="H13" s="14" t="s">
         <v>170</v>
       </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
@@ -1961,13 +1992,26 @@
       <c r="C14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="D14" s="11">
+        <v>14</v>
+      </c>
+      <c r="E14" s="11">
+        <v>14</v>
+      </c>
+      <c r="F14" s="11">
+        <v>14</v>
+      </c>
+      <c r="G14" s="11">
+        <v>10</v>
+      </c>
       <c r="H14" s="14" t="s">
         <v>171</v>
       </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
@@ -1979,13 +2023,26 @@
       <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="D15" s="11">
+        <v>14</v>
+      </c>
+      <c r="E15" s="11">
+        <v>12</v>
+      </c>
+      <c r="F15" s="11">
+        <v>11</v>
+      </c>
+      <c r="G15" s="11">
+        <v>13</v>
+      </c>
       <c r="H15" s="14" t="s">
         <v>172</v>
       </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
@@ -1997,15 +2054,28 @@
       <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="D16" s="11">
+        <v>9</v>
+      </c>
+      <c r="E16" s="11">
+        <v>6</v>
+      </c>
+      <c r="F16" s="11">
+        <v>10</v>
+      </c>
+      <c r="G16" s="11">
+        <v>13</v>
+      </c>
       <c r="H16" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>6</v>
       </c>
@@ -2015,15 +2085,28 @@
       <c r="C17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="D17" s="11">
+        <v>16</v>
+      </c>
+      <c r="E17" s="11">
+        <v>13</v>
+      </c>
+      <c r="F17" s="11">
+        <v>15</v>
+      </c>
+      <c r="G17" s="11">
+        <v>14</v>
+      </c>
       <c r="H17" s="14" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>7</v>
       </c>
@@ -2033,15 +2116,28 @@
       <c r="C18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="D18" s="11">
+        <v>16</v>
+      </c>
+      <c r="E18" s="11">
+        <v>14</v>
+      </c>
+      <c r="F18" s="11">
+        <v>16</v>
+      </c>
+      <c r="G18" s="11">
+        <v>4</v>
+      </c>
       <c r="H18" s="14" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>8</v>
       </c>
@@ -2051,15 +2147,28 @@
       <c r="C19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>5</v>
+      </c>
+      <c r="F19" s="11">
+        <v>6</v>
+      </c>
+      <c r="G19" s="11">
+        <v>2</v>
+      </c>
       <c r="H19" s="14" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>9</v>
       </c>
@@ -2069,15 +2178,28 @@
       <c r="C20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="D20" s="11">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11">
+        <v>4</v>
+      </c>
+      <c r="G20" s="11">
+        <v>10</v>
+      </c>
       <c r="H20" s="14" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>10</v>
       </c>
@@ -2087,15 +2209,28 @@
       <c r="C21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="D21" s="11">
+        <v>10</v>
+      </c>
+      <c r="E21" s="11">
+        <v>4</v>
+      </c>
+      <c r="F21" s="11">
+        <v>10</v>
+      </c>
+      <c r="G21" s="11">
+        <v>8</v>
+      </c>
       <c r="H21" s="14" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>11</v>
       </c>
@@ -2105,15 +2240,28 @@
       <c r="C22" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="D22" s="11">
+        <v>9</v>
+      </c>
+      <c r="E22" s="11">
+        <v>12</v>
+      </c>
+      <c r="F22" s="11">
+        <v>4</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
       <c r="H22" s="14" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>12</v>
       </c>
@@ -2123,15 +2271,28 @@
       <c r="C23" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="D23" s="11">
+        <v>13</v>
+      </c>
+      <c r="E23" s="11">
+        <v>16</v>
+      </c>
+      <c r="F23" s="11">
+        <v>15</v>
+      </c>
+      <c r="G23" s="11">
+        <v>14</v>
+      </c>
       <c r="H23" s="14" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>13</v>
       </c>
@@ -2141,15 +2302,28 @@
       <c r="C24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="D24" s="11">
+        <v>13</v>
+      </c>
+      <c r="E24" s="11">
+        <v>14</v>
+      </c>
+      <c r="F24" s="11">
+        <v>15</v>
+      </c>
+      <c r="G24" s="11">
+        <v>10</v>
+      </c>
       <c r="H24" s="14" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>14</v>
       </c>
@@ -2159,15 +2333,28 @@
       <c r="C25" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
+      <c r="D25" s="11">
+        <v>6</v>
+      </c>
+      <c r="E25" s="11">
+        <v>12</v>
+      </c>
+      <c r="F25" s="11">
+        <v>6</v>
+      </c>
+      <c r="G25" s="11">
+        <v>12</v>
+      </c>
       <c r="H25" s="14" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>15</v>
       </c>
@@ -2177,15 +2364,28 @@
       <c r="C26" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
+      <c r="D26" s="11">
+        <v>16</v>
+      </c>
+      <c r="E26" s="11">
+        <v>13</v>
+      </c>
+      <c r="F26" s="11">
+        <v>12</v>
+      </c>
+      <c r="G26" s="11">
+        <v>16</v>
+      </c>
       <c r="H26" s="14" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>16</v>
       </c>
@@ -2195,15 +2395,28 @@
       <c r="C27" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
+      <c r="D27" s="11">
+        <v>14</v>
+      </c>
+      <c r="E27" s="11">
+        <v>11</v>
+      </c>
+      <c r="F27" s="11">
+        <v>16</v>
+      </c>
+      <c r="G27" s="11">
+        <v>14</v>
+      </c>
       <c r="H27" s="14" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>17</v>
       </c>
@@ -2213,15 +2426,28 @@
       <c r="C28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
+      <c r="D28" s="11">
+        <v>15</v>
+      </c>
+      <c r="E28" s="11">
+        <v>9</v>
+      </c>
+      <c r="F28" s="11">
+        <v>13</v>
+      </c>
+      <c r="G28" s="11">
+        <v>8</v>
+      </c>
       <c r="H28" s="14" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>18</v>
       </c>
@@ -2231,15 +2457,28 @@
       <c r="C29" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
+      <c r="D29" s="11">
+        <v>14</v>
+      </c>
+      <c r="E29" s="11">
+        <v>13</v>
+      </c>
+      <c r="F29" s="11">
+        <v>15</v>
+      </c>
+      <c r="G29" s="11">
+        <v>12</v>
+      </c>
       <c r="H29" s="14" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>19</v>
       </c>
@@ -2249,15 +2488,28 @@
       <c r="C30" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
+      <c r="D30" s="11">
+        <v>10</v>
+      </c>
+      <c r="E30" s="11">
+        <v>10</v>
+      </c>
+      <c r="F30" s="11">
+        <v>12</v>
+      </c>
+      <c r="G30" s="11">
+        <v>16</v>
+      </c>
       <c r="H30" s="14" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>20</v>
       </c>
@@ -2267,15 +2519,28 @@
       <c r="C31" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
+      <c r="D31" s="11">
+        <v>12</v>
+      </c>
+      <c r="E31" s="11">
+        <v>4</v>
+      </c>
+      <c r="F31" s="11">
+        <v>8</v>
+      </c>
+      <c r="G31" s="11">
+        <v>8</v>
+      </c>
       <c r="H31" s="14" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>21</v>
       </c>
@@ -2285,15 +2550,28 @@
       <c r="C32" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
+      <c r="D32" s="11">
+        <v>11</v>
+      </c>
+      <c r="E32" s="11">
+        <v>12</v>
+      </c>
+      <c r="F32" s="11">
+        <v>15</v>
+      </c>
+      <c r="G32" s="11">
+        <v>13.5</v>
+      </c>
       <c r="H32" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>22</v>
       </c>
@@ -2303,15 +2581,28 @@
       <c r="C33" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
+      <c r="D33" s="11">
+        <v>14</v>
+      </c>
+      <c r="E33" s="11">
+        <v>12</v>
+      </c>
+      <c r="F33" s="11">
+        <v>16</v>
+      </c>
+      <c r="G33" s="11">
+        <v>16</v>
+      </c>
       <c r="H33" s="14" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>23</v>
       </c>
@@ -2321,15 +2612,28 @@
       <c r="C34" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+      <c r="D34" s="11">
+        <v>14</v>
+      </c>
+      <c r="E34" s="11">
+        <v>8</v>
+      </c>
+      <c r="F34" s="11">
+        <v>16</v>
+      </c>
+      <c r="G34" s="11">
+        <v>14</v>
+      </c>
       <c r="H34" s="14" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>24</v>
       </c>
@@ -2339,15 +2643,28 @@
       <c r="C35" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+      <c r="D35" s="11">
+        <v>14</v>
+      </c>
+      <c r="E35" s="11">
+        <v>4</v>
+      </c>
+      <c r="F35" s="11">
+        <v>14</v>
+      </c>
+      <c r="G35" s="11">
+        <v>11.5</v>
+      </c>
       <c r="H35" s="14" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>25</v>
       </c>
@@ -2357,15 +2674,28 @@
       <c r="C36" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="D36" s="11">
+        <v>3</v>
+      </c>
+      <c r="E36" s="11">
+        <v>6</v>
+      </c>
+      <c r="F36" s="11">
+        <v>6</v>
+      </c>
+      <c r="G36" s="11">
+        <v>7</v>
+      </c>
       <c r="H36" s="14" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>26</v>
       </c>
@@ -2375,15 +2705,28 @@
       <c r="C37" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
+      <c r="D37" s="11">
+        <v>12</v>
+      </c>
+      <c r="E37" s="11">
+        <v>14</v>
+      </c>
+      <c r="F37" s="11">
+        <v>15</v>
+      </c>
+      <c r="G37" s="11">
+        <v>13</v>
+      </c>
       <c r="H37" s="14" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>27</v>
       </c>
@@ -2393,15 +2736,28 @@
       <c r="C38" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="D38" s="11">
+        <v>14</v>
+      </c>
+      <c r="E38" s="11">
+        <v>8</v>
+      </c>
+      <c r="F38" s="11">
+        <v>13</v>
+      </c>
+      <c r="G38" s="11">
+        <v>14</v>
+      </c>
       <c r="H38" s="14" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>28</v>
       </c>
@@ -2411,15 +2767,28 @@
       <c r="C39" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="D39" s="11">
+        <v>15</v>
+      </c>
+      <c r="E39" s="11">
+        <v>12</v>
+      </c>
+      <c r="F39" s="11">
+        <v>14</v>
+      </c>
+      <c r="G39" s="11">
+        <v>6</v>
+      </c>
       <c r="H39" s="14" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -2429,15 +2798,28 @@
       <c r="C40" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="D40" s="11">
+        <v>14</v>
+      </c>
+      <c r="E40" s="11">
+        <v>13</v>
+      </c>
+      <c r="F40" s="11">
+        <v>15</v>
+      </c>
+      <c r="G40" s="11">
+        <v>13.5</v>
+      </c>
       <c r="H40" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -2447,15 +2829,28 @@
       <c r="C41" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
+      <c r="D41" s="11">
+        <v>11</v>
+      </c>
+      <c r="E41" s="11">
+        <v>11</v>
+      </c>
+      <c r="F41" s="11">
+        <v>9</v>
+      </c>
+      <c r="G41" s="11">
+        <v>9</v>
+      </c>
       <c r="H41" s="14" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>31</v>
       </c>
@@ -2465,15 +2860,28 @@
       <c r="C42" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="D42" s="11">
+        <v>11</v>
+      </c>
+      <c r="E42" s="11">
+        <v>7</v>
+      </c>
+      <c r="F42" s="11">
+        <v>13</v>
+      </c>
+      <c r="G42" s="11">
+        <v>11</v>
+      </c>
       <c r="H42" s="14" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>32</v>
       </c>
@@ -2483,15 +2891,28 @@
       <c r="C43" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="D43" s="11">
+        <v>11</v>
+      </c>
+      <c r="E43" s="11">
+        <v>14</v>
+      </c>
+      <c r="F43" s="11">
+        <v>16</v>
+      </c>
+      <c r="G43" s="11">
+        <v>11</v>
+      </c>
       <c r="H43" s="14" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>33</v>
       </c>
@@ -2501,15 +2922,28 @@
       <c r="C44" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
+      <c r="D44" s="11">
+        <v>16</v>
+      </c>
+      <c r="E44" s="11">
+        <v>12</v>
+      </c>
+      <c r="F44" s="11">
+        <v>14</v>
+      </c>
+      <c r="G44" s="11">
+        <v>9.5</v>
+      </c>
       <c r="H44" s="15" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>34</v>
       </c>
@@ -2519,15 +2953,28 @@
       <c r="C45" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
+      <c r="D45" s="11">
+        <v>16</v>
+      </c>
+      <c r="E45" s="11">
+        <v>15</v>
+      </c>
+      <c r="F45" s="11">
+        <v>16</v>
+      </c>
+      <c r="G45" s="11">
+        <v>10</v>
+      </c>
       <c r="H45" s="14" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>35</v>
       </c>
@@ -2537,15 +2984,28 @@
       <c r="C46" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
+      <c r="D46" s="11">
+        <v>14</v>
+      </c>
+      <c r="E46" s="11">
+        <v>12</v>
+      </c>
+      <c r="F46" s="11">
+        <v>14</v>
+      </c>
+      <c r="G46" s="11">
+        <v>8</v>
+      </c>
       <c r="H46" s="14" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>36</v>
       </c>
@@ -2555,15 +3015,28 @@
       <c r="C47" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
+      <c r="D47" s="11">
+        <v>16</v>
+      </c>
+      <c r="E47" s="11">
+        <v>16</v>
+      </c>
+      <c r="F47" s="11">
+        <v>14</v>
+      </c>
+      <c r="G47" s="11">
+        <v>9</v>
+      </c>
       <c r="H47" s="14" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>37</v>
       </c>
@@ -2573,15 +3046,28 @@
       <c r="C48" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="D48" s="11">
+        <v>16</v>
+      </c>
+      <c r="E48" s="11">
+        <v>13</v>
+      </c>
+      <c r="F48" s="11">
+        <v>15</v>
+      </c>
+      <c r="G48" s="11">
+        <v>15.5</v>
+      </c>
       <c r="H48" s="14" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>38</v>
       </c>
@@ -2591,15 +3077,28 @@
       <c r="C49" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
+      <c r="D49" s="11">
+        <v>16</v>
+      </c>
+      <c r="E49" s="11">
+        <v>16</v>
+      </c>
+      <c r="F49" s="11">
+        <v>14</v>
+      </c>
+      <c r="G49" s="11">
+        <v>14</v>
+      </c>
       <c r="H49" s="14" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>39</v>
       </c>
@@ -2609,15 +3108,28 @@
       <c r="C50" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
+      <c r="D50" s="11">
+        <v>13</v>
+      </c>
+      <c r="E50" s="11">
+        <v>9</v>
+      </c>
+      <c r="F50" s="11">
+        <v>11</v>
+      </c>
+      <c r="G50" s="11">
+        <v>14</v>
+      </c>
       <c r="H50" s="14" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <v>40</v>
       </c>
@@ -2627,15 +3139,28 @@
       <c r="C51" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
+      <c r="D51" s="11">
+        <v>8</v>
+      </c>
+      <c r="E51" s="11">
+        <v>2</v>
+      </c>
+      <c r="F51" s="11">
+        <v>4</v>
+      </c>
+      <c r="G51" s="11">
+        <v>10.5</v>
+      </c>
       <c r="H51" s="14" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>41</v>
       </c>
@@ -2645,15 +3170,28 @@
       <c r="C52" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
+      <c r="D52" s="11">
+        <v>12</v>
+      </c>
+      <c r="E52" s="11">
+        <v>12</v>
+      </c>
+      <c r="F52" s="11">
+        <v>5</v>
+      </c>
+      <c r="G52" s="11">
+        <v>3</v>
+      </c>
       <c r="H52" s="14" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="11">
         <v>42</v>
       </c>
@@ -2663,15 +3201,28 @@
       <c r="C53" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
+      <c r="D53" s="11">
+        <v>16</v>
+      </c>
+      <c r="E53" s="11">
+        <v>8</v>
+      </c>
+      <c r="F53" s="11">
+        <v>16</v>
+      </c>
+      <c r="G53" s="11">
+        <v>16</v>
+      </c>
       <c r="H53" s="14" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>43</v>
       </c>
@@ -2681,15 +3232,28 @@
       <c r="C54" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
+      <c r="D54" s="11">
+        <v>10</v>
+      </c>
+      <c r="E54" s="11">
+        <v>5</v>
+      </c>
+      <c r="F54" s="11">
+        <v>10</v>
+      </c>
+      <c r="G54" s="11">
+        <v>11</v>
+      </c>
       <c r="H54" s="14" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>44</v>
       </c>
@@ -2699,15 +3263,28 @@
       <c r="C55" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
+      <c r="D55" s="11">
+        <v>11</v>
+      </c>
+      <c r="E55" s="11">
+        <v>16</v>
+      </c>
+      <c r="F55" s="11">
+        <v>16</v>
+      </c>
+      <c r="G55" s="11">
+        <v>15</v>
+      </c>
       <c r="H55" s="14" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>45</v>
       </c>
@@ -2717,15 +3294,28 @@
       <c r="C56" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
+      <c r="D56" s="11">
+        <v>6</v>
+      </c>
+      <c r="E56" s="11">
+        <v>6</v>
+      </c>
+      <c r="F56" s="11">
+        <v>14</v>
+      </c>
+      <c r="G56" s="11">
+        <v>8</v>
+      </c>
       <c r="H56" s="14" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="11">
         <v>46</v>
       </c>
@@ -2735,15 +3325,28 @@
       <c r="C57" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
+      <c r="D57" s="11">
+        <v>15</v>
+      </c>
+      <c r="E57" s="11">
+        <v>10</v>
+      </c>
+      <c r="F57" s="11">
+        <v>13</v>
+      </c>
+      <c r="G57" s="11">
+        <v>14</v>
+      </c>
       <c r="H57" s="14" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>47</v>
       </c>
@@ -2753,15 +3356,28 @@
       <c r="C58" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
+      <c r="D58" s="11">
+        <v>15</v>
+      </c>
+      <c r="E58" s="11">
+        <v>16</v>
+      </c>
+      <c r="F58" s="11">
+        <v>16</v>
+      </c>
+      <c r="G58" s="11">
+        <v>14.5</v>
+      </c>
       <c r="H58" s="14" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
         <v>48</v>
       </c>
@@ -2771,15 +3387,28 @@
       <c r="C59" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
+      <c r="D59" s="11">
+        <v>14</v>
+      </c>
+      <c r="E59" s="11">
+        <v>5</v>
+      </c>
+      <c r="F59" s="11">
+        <v>9</v>
+      </c>
+      <c r="G59" s="11">
+        <v>10.5</v>
+      </c>
       <c r="H59" s="14" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>49</v>
       </c>
@@ -2789,15 +3418,28 @@
       <c r="C60" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
+      <c r="D60" s="11">
+        <v>15</v>
+      </c>
+      <c r="E60" s="11">
+        <v>13</v>
+      </c>
+      <c r="F60" s="11">
+        <v>13</v>
+      </c>
+      <c r="G60" s="11">
+        <v>12.5</v>
+      </c>
       <c r="H60" s="14" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="11">
         <v>50</v>
       </c>
@@ -2807,15 +3449,28 @@
       <c r="C61" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
+      <c r="D61" s="11">
+        <v>15</v>
+      </c>
+      <c r="E61" s="11">
+        <v>15</v>
+      </c>
+      <c r="F61" s="11">
+        <v>15</v>
+      </c>
+      <c r="G61" s="11">
+        <v>12</v>
+      </c>
       <c r="H61" s="14" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>51</v>
       </c>
@@ -2825,15 +3480,28 @@
       <c r="C62" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
+      <c r="D62" s="11">
+        <v>16</v>
+      </c>
+      <c r="E62" s="11">
+        <v>16</v>
+      </c>
+      <c r="F62" s="11">
+        <v>16</v>
+      </c>
+      <c r="G62" s="11">
+        <v>1</v>
+      </c>
       <c r="H62" s="14" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="11">
         <v>52</v>
       </c>
@@ -2843,15 +3511,28 @@
       <c r="C63" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
+      <c r="D63" s="11">
+        <v>13</v>
+      </c>
+      <c r="E63" s="11">
+        <v>7</v>
+      </c>
+      <c r="F63" s="11">
+        <v>8</v>
+      </c>
+      <c r="G63" s="11">
+        <v>12.5</v>
+      </c>
       <c r="H63" s="14" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>53</v>
       </c>
@@ -2861,15 +3542,28 @@
       <c r="C64" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
+      <c r="D64" s="11">
+        <v>12</v>
+      </c>
+      <c r="E64" s="11">
+        <v>10</v>
+      </c>
+      <c r="F64" s="11">
+        <v>13</v>
+      </c>
+      <c r="G64" s="11">
+        <v>14.5</v>
+      </c>
       <c r="H64" s="14" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="11">
         <v>54</v>
       </c>
@@ -2879,15 +3573,28 @@
       <c r="C65" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
+      <c r="D65" s="11">
+        <v>12</v>
+      </c>
+      <c r="E65" s="11">
+        <v>7</v>
+      </c>
+      <c r="F65" s="11">
+        <v>4</v>
+      </c>
+      <c r="G65" s="11">
+        <v>5.5</v>
+      </c>
       <c r="H65" s="14" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>55</v>
       </c>
@@ -2897,15 +3604,28 @@
       <c r="C66" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
+      <c r="D66" s="11">
+        <v>12</v>
+      </c>
+      <c r="E66" s="11">
+        <v>14</v>
+      </c>
+      <c r="F66" s="11">
+        <v>6</v>
+      </c>
+      <c r="G66" s="11">
+        <v>7.5</v>
+      </c>
       <c r="H66" s="14" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="11">
         <v>56</v>
       </c>
@@ -2915,15 +3635,28 @@
       <c r="C67" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
+      <c r="D67" s="11">
+        <v>13</v>
+      </c>
+      <c r="E67" s="11">
+        <v>5</v>
+      </c>
+      <c r="F67" s="11">
+        <v>12</v>
+      </c>
+      <c r="G67" s="11">
+        <v>4.5</v>
+      </c>
       <c r="H67" s="14" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>57</v>
       </c>
@@ -2933,15 +3666,28 @@
       <c r="C68" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
+      <c r="D68" s="11">
+        <v>5</v>
+      </c>
+      <c r="E68" s="11">
+        <v>6</v>
+      </c>
+      <c r="F68" s="11">
+        <v>2</v>
+      </c>
+      <c r="G68" s="11">
+        <v>8.5</v>
+      </c>
       <c r="H68" s="14" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="11">
         <v>58</v>
       </c>
@@ -2951,15 +3697,28 @@
       <c r="C69" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
+      <c r="D69" s="11">
+        <v>15</v>
+      </c>
+      <c r="E69" s="11">
+        <v>13</v>
+      </c>
+      <c r="F69" s="11">
+        <v>11</v>
+      </c>
+      <c r="G69" s="11">
+        <v>10</v>
+      </c>
       <c r="H69" s="14" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
         <v>59</v>
       </c>
@@ -2969,15 +3728,28 @@
       <c r="C70" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
+      <c r="D70" s="11">
+        <v>12</v>
+      </c>
+      <c r="E70" s="11">
+        <v>11</v>
+      </c>
+      <c r="F70" s="11">
+        <v>8</v>
+      </c>
+      <c r="G70" s="11">
+        <v>15</v>
+      </c>
       <c r="H70" s="15" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="11">
         <v>60</v>
       </c>
@@ -2987,15 +3759,28 @@
       <c r="C71" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
+      <c r="D71" s="11">
+        <v>8</v>
+      </c>
+      <c r="E71" s="11">
+        <v>10</v>
+      </c>
+      <c r="F71" s="11">
+        <v>8</v>
+      </c>
+      <c r="G71" s="11">
+        <v>7</v>
+      </c>
       <c r="H71" s="14" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
         <v>61</v>
       </c>
@@ -3005,15 +3790,28 @@
       <c r="C72" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
+      <c r="D72" s="11">
+        <v>15</v>
+      </c>
+      <c r="E72" s="11">
+        <v>12</v>
+      </c>
+      <c r="F72" s="11">
+        <v>11</v>
+      </c>
+      <c r="G72" s="11">
+        <v>10</v>
+      </c>
       <c r="H72" s="14" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="11">
         <v>62</v>
       </c>
@@ -3023,15 +3821,28 @@
       <c r="C73" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
+      <c r="D73" s="11">
+        <v>13</v>
+      </c>
+      <c r="E73" s="11">
+        <v>12</v>
+      </c>
+      <c r="F73" s="11">
+        <v>16</v>
+      </c>
+      <c r="G73" s="11">
+        <v>11</v>
+      </c>
       <c r="H73" s="14" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>63</v>
       </c>
@@ -3041,15 +3852,28 @@
       <c r="C74" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
+      <c r="D74" s="11">
+        <v>12</v>
+      </c>
+      <c r="E74" s="11">
+        <v>14</v>
+      </c>
+      <c r="F74" s="11">
+        <v>15</v>
+      </c>
+      <c r="G74" s="11">
+        <v>13</v>
+      </c>
       <c r="H74" s="14" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="11">
         <v>64</v>
       </c>
@@ -3059,15 +3883,28 @@
       <c r="C75" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
+      <c r="D75" s="11">
+        <v>10</v>
+      </c>
+      <c r="E75" s="11">
+        <v>10</v>
+      </c>
+      <c r="F75" s="11">
+        <v>12</v>
+      </c>
+      <c r="G75" s="11">
+        <v>13.5</v>
+      </c>
       <c r="H75" s="14" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
         <v>65</v>
       </c>
@@ -3077,15 +3914,28 @@
       <c r="C76" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
+      <c r="D76" s="11">
+        <v>16</v>
+      </c>
+      <c r="E76" s="11">
+        <v>12</v>
+      </c>
+      <c r="F76" s="11">
+        <v>13</v>
+      </c>
+      <c r="G76" s="11">
+        <v>9</v>
+      </c>
       <c r="H76" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="11">
         <v>66</v>
       </c>
@@ -3095,15 +3945,28 @@
       <c r="C77" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
+      <c r="D77" s="11">
+        <v>12</v>
+      </c>
+      <c r="E77" s="11">
+        <v>13</v>
+      </c>
+      <c r="F77" s="11">
+        <v>13</v>
+      </c>
+      <c r="G77" s="11">
+        <v>15</v>
+      </c>
       <c r="H77" s="14" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
         <v>67</v>
       </c>
@@ -3113,15 +3976,28 @@
       <c r="C78" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
+      <c r="D78" s="11">
+        <v>16</v>
+      </c>
+      <c r="E78" s="11">
+        <v>14</v>
+      </c>
+      <c r="F78" s="11">
+        <v>15</v>
+      </c>
+      <c r="G78" s="11">
+        <v>12.5</v>
+      </c>
       <c r="H78" s="14" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="11">
         <v>68</v>
       </c>
@@ -3131,15 +4007,28 @@
       <c r="C79" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
+      <c r="D79" s="11">
+        <v>12</v>
+      </c>
+      <c r="E79" s="11">
+        <v>13</v>
+      </c>
+      <c r="F79" s="11">
+        <v>11</v>
+      </c>
+      <c r="G79" s="11">
+        <v>10.5</v>
+      </c>
       <c r="H79" s="14" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
         <v>69</v>
       </c>
@@ -3149,15 +4038,28 @@
       <c r="C80" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
+      <c r="D80" s="11">
+        <v>6</v>
+      </c>
+      <c r="E80" s="11">
+        <v>9</v>
+      </c>
+      <c r="F80" s="11">
+        <v>14</v>
+      </c>
+      <c r="G80" s="11">
+        <v>3.5</v>
+      </c>
       <c r="H80" s="14" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="11">
         <v>70</v>
       </c>
@@ -3167,15 +4069,28 @@
       <c r="C81" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
+      <c r="D81" s="11">
+        <v>2</v>
+      </c>
+      <c r="E81" s="11">
+        <v>16</v>
+      </c>
+      <c r="F81" s="11">
+        <v>2</v>
+      </c>
+      <c r="G81" s="11">
+        <v>3</v>
+      </c>
       <c r="H81" s="14" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>71</v>
       </c>
@@ -3185,15 +4100,28 @@
       <c r="C82" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
+      <c r="D82" s="11">
+        <v>4</v>
+      </c>
+      <c r="E82" s="11">
+        <v>11</v>
+      </c>
+      <c r="F82" s="11">
+        <v>12</v>
+      </c>
+      <c r="G82" s="11">
+        <v>8</v>
+      </c>
       <c r="H82" s="14" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="11">
         <v>72</v>
       </c>
@@ -3203,15 +4131,28 @@
       <c r="C83" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
+      <c r="D83" s="11">
+        <v>9</v>
+      </c>
+      <c r="E83" s="11">
+        <v>12</v>
+      </c>
+      <c r="F83" s="11">
+        <v>12</v>
+      </c>
+      <c r="G83" s="11">
+        <v>6</v>
+      </c>
       <c r="H83" s="14" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>73</v>
       </c>
@@ -3221,15 +4162,28 @@
       <c r="C84" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
+      <c r="D84" s="11">
+        <v>14</v>
+      </c>
+      <c r="E84" s="11">
+        <v>16</v>
+      </c>
+      <c r="F84" s="11">
+        <v>12</v>
+      </c>
+      <c r="G84" s="11">
+        <v>0</v>
+      </c>
       <c r="H84" s="14" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
         <v>74</v>
       </c>
@@ -3239,15 +4193,28 @@
       <c r="C85" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
+      <c r="D85" s="11">
+        <v>10</v>
+      </c>
+      <c r="E85" s="11">
+        <v>7</v>
+      </c>
+      <c r="F85" s="11">
+        <v>0</v>
+      </c>
+      <c r="G85" s="11">
+        <v>0</v>
+      </c>
       <c r="H85" s="14" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>75</v>
       </c>
@@ -3257,13 +4224,26 @@
       <c r="C86" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
+      <c r="D86" s="11">
+        <v>16</v>
+      </c>
+      <c r="E86" s="11">
+        <v>12</v>
+      </c>
+      <c r="F86" s="11">
+        <v>10</v>
+      </c>
+      <c r="G86" s="11">
+        <v>7</v>
+      </c>
       <c r="H86" s="14" t="s">
         <v>243</v>
       </c>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="13">
